--- a/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
+++ b/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -607,7 +607,7 @@
         <v>已上线</v>
       </c>
       <c r="E12" t="str">
-        <v>已安装待推流</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -734,10 +734,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>创善烧鹅</v>
+        <v>窄巷口</v>
       </c>
       <c r="C20" t="str">
-        <v>广州市越秀区百煜餐饮店（个体工商户）</v>
+        <v>广州市越秀区华记美食店（个体工商户）</v>
       </c>
       <c r="D20" t="str">
         <v>已上线</v>
@@ -751,16 +751,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>炭火匠人</v>
+        <v>创善烧鹅</v>
       </c>
       <c r="C21" t="str">
-        <v>广州市越秀区万欢千膳餐饮店（个体工商户）</v>
+        <v>广州市越秀区百煜餐饮店（个体工商户）</v>
       </c>
       <c r="D21" t="str">
         <v>已上线</v>
       </c>
       <c r="E21" t="str">
-        <v>电信已推流但市监局看不到，核查中</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -768,10 +768,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>西华美食·老广烧腊(百灵路店)</v>
+        <v>炭火匠人</v>
       </c>
       <c r="C22" t="str">
-        <v>广州市西华美食品有限公司第一分店</v>
+        <v>广州市越秀区万欢千膳餐饮店（个体工商户）</v>
       </c>
       <c r="D22" t="str">
         <v>已上线</v>
@@ -785,10 +785,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>盘福路荔银肠粉店</v>
+        <v>西华美食·老广烧腊(百灵路店)</v>
       </c>
       <c r="C23" t="str">
-        <v>广州港旗餐饮管理有限公司</v>
+        <v>广州市西华美食品有限公司第一分店</v>
       </c>
       <c r="D23" t="str">
         <v>已上线</v>
@@ -802,10 +802,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>小东北</v>
+        <v>盘福路荔银肠粉店</v>
       </c>
       <c r="C24" t="str">
-        <v>广州市越秀区咱家饺子坊</v>
+        <v>广州港旗餐饮管理有限公司</v>
       </c>
       <c r="D24" t="str">
         <v>已上线</v>
@@ -819,10 +819,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>广州市越秀区味鲜小馆</v>
+        <v>小东北</v>
       </c>
       <c r="C25" t="str">
-        <v>广州市越秀区味鲜小馆（个体工商户）</v>
+        <v>广州市越秀区咱家饺子坊</v>
       </c>
       <c r="D25" t="str">
         <v>已上线</v>
@@ -836,16 +836,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>广州市越秀区滋味水饺店</v>
+        <v>广潮仔</v>
       </c>
       <c r="C26" t="str">
-        <v>广州市越秀区滋味水饺店（个体工商户）</v>
+        <v>广州市越秀区远记广潮仔海鲜馆（个体工商户）</v>
       </c>
       <c r="D26" t="str">
         <v>已上线</v>
       </c>
       <c r="E26" t="str">
-        <v>电信已推流但市监局看不到，核查中</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -853,10 +853,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>广州市越秀区福华顺美食店</v>
+        <v>潮汕壹粉道</v>
       </c>
       <c r="C27" t="str">
-        <v>广州市越秀区福华顺美食店（个体工商户）</v>
+        <v>广州市越秀区峰玲小食档（个体工商户）</v>
       </c>
       <c r="D27" t="str">
         <v>已上线</v>
@@ -870,16 +870,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>元气饭堂</v>
+        <v>广州市越秀区味鲜小馆</v>
       </c>
       <c r="C28" t="str">
-        <v>广州市豪哥烧腊有限公司</v>
+        <v>广州市越秀区味鲜小馆（个体工商户）</v>
       </c>
       <c r="D28" t="str">
         <v>已上线</v>
       </c>
       <c r="E28" t="str">
-        <v>电信已推流但市监局看不到，核查中</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -887,10 +887,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>新泰乐</v>
+        <v>广州市越秀区滋味水饺店</v>
       </c>
       <c r="C29" t="str">
-        <v>广州市越秀区盘福新泰乐菜馆</v>
+        <v>广州市越秀区滋味水饺店（个体工商户）</v>
       </c>
       <c r="D29" t="str">
         <v>已上线</v>
@@ -904,10 +904,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>顺德牛花猪杂粥</v>
+        <v>广州市越秀区福华顺美食店</v>
       </c>
       <c r="C30" t="str">
-        <v>广州市越秀区捌记美食店（个体工商户）</v>
+        <v>广州市越秀区福华顺美食店（个体工商户）</v>
       </c>
       <c r="D30" t="str">
         <v>已上线</v>
@@ -921,10 +921,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>布豆咖啡</v>
+        <v>元气饭堂</v>
       </c>
       <c r="C31" t="str">
-        <v>广州市越秀区布豆食品店（个体工商户）</v>
+        <v>广州市豪哥烧腊有限公司</v>
       </c>
       <c r="D31" t="str">
         <v>已上线</v>
@@ -938,10 +938,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>广州市越秀区市壹餐饮店（个体工商户）（荔银肠粉）</v>
+        <v>新泰乐</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>广州市越秀区盘福新泰乐菜馆</v>
       </c>
       <c r="D32" t="str">
         <v>已上线</v>
@@ -952,33 +952,33 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>吞口熊</v>
+        <v>顺德牛花猪杂粥</v>
       </c>
       <c r="C33" t="str">
-        <v>广州市越秀区江南粥铺</v>
+        <v>广州市越秀区捌记美食店（个体工商户）</v>
       </c>
       <c r="D33" t="str">
-        <v>用户拒绝</v>
+        <v>已上线</v>
       </c>
       <c r="E33" t="str">
-        <v>已关门</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>叫了只炸鸡</v>
+        <v>布豆咖啡</v>
       </c>
       <c r="C34" t="str">
-        <v>广州市越秀区童杨食品店</v>
+        <v>广州市越秀区布豆食品店（个体工商户）</v>
       </c>
       <c r="D34" t="str">
-        <v>用户拒绝</v>
+        <v>已上线</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -986,194 +986,194 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>囍膳小厨 养生汤</v>
+        <v>广州市越秀区市壹餐饮店（个体工商户）（荔银肠粉）</v>
       </c>
       <c r="C35" t="str">
-        <v>广州粤喜膳餐饮管理有限公司</v>
+        <v>广州市越秀区市壹餐饮店（个体工商户）</v>
       </c>
       <c r="D35" t="str">
-        <v>用户拒绝</v>
+        <v>已上线</v>
       </c>
       <c r="E35" t="str">
-        <v>二次联系后客户拒绝办理</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B36" t="str">
-        <v>广州港意头餐饮服务工作室</v>
+        <v>吞口熊</v>
       </c>
       <c r="C36" t="str">
-        <v>广州港意头餐饮服务工作室（个人独资）</v>
+        <v>广州市越秀区江南粥铺</v>
       </c>
       <c r="D36" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E36" t="str">
-        <v>已拒绝</v>
+        <v>已关门</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B37" t="str">
-        <v>广州市越秀区盛裕餐饮店</v>
+        <v>叫了只炸鸡</v>
       </c>
       <c r="C37" t="str">
-        <v>广州市越秀区盛裕餐饮店</v>
+        <v>广州市越秀区童杨食品店</v>
       </c>
       <c r="D37" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E37" t="str">
-        <v>客户反映已经有人帮他装了</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B38" t="str">
-        <v>王富贵（广州）餐饮管理服务有限公司</v>
+        <v>囍膳小厨 养生汤</v>
       </c>
       <c r="C38" t="str">
-        <v>王富贵（广州）餐饮管理服务有限公司</v>
+        <v>广州粤喜膳餐饮管理有限公司</v>
       </c>
       <c r="D38" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E38" t="str">
-        <v>已转荔湾跟进</v>
+        <v>二次联系后客户拒绝办理</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B39" t="str">
-        <v>肥俊牛肉饭</v>
+        <v>广州港意头餐饮服务工作室</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>广州港意头餐饮服务工作室（个人独资）</v>
       </c>
       <c r="D39" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E39" t="str">
-        <v>已转荔湾跟进</v>
+        <v>已拒绝</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B40" t="str">
-        <v>华辉拉肠</v>
+        <v>广州市越秀区盛裕餐饮店</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>广州市越秀区盛裕餐饮店</v>
       </c>
       <c r="D40" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E40" t="str">
-        <v>等集团统一通知</v>
+        <v>客户反映已经有人帮他装了</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B41" t="str">
-        <v>广州市越秀区遇见老袁馅饼店</v>
+        <v>王富贵（广州）餐饮管理服务有限公司</v>
       </c>
       <c r="C41" t="str">
-        <v>广州市越秀区遇见老袁馅饼店（个体工商户）</v>
+        <v>王富贵（广州）餐饮管理服务有限公司</v>
       </c>
       <c r="D41" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E41" t="str">
-        <v>医国街全部要求装再装</v>
+        <v>已转荔湾跟进</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B42" t="str">
-        <v>威笑鸡煲档</v>
+        <v>肥俊牛肉饭</v>
       </c>
       <c r="C42" t="str">
-        <v>广州市越秀区威笑鸡煲档（个体工商户）</v>
+        <v/>
       </c>
       <c r="D42" t="str">
-        <v>已安装</v>
+        <v>用户拒绝</v>
       </c>
       <c r="E42" t="str">
-        <v>需荔湾整改，已填待推流</v>
+        <v>已转荔湾跟进</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B43" t="str">
-        <v>窄巷口</v>
+        <v>华辉拉肠</v>
       </c>
       <c r="C43" t="str">
-        <v>广州市越秀区华记美食店(个体工商户)</v>
+        <v/>
       </c>
       <c r="D43" t="str">
-        <v>已安装</v>
+        <v>用户拒绝</v>
       </c>
       <c r="E43" t="str">
-        <v>已填资料待推流</v>
+        <v>等集团统一通知</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B44" t="str">
-        <v>广潮仔</v>
+        <v>广州市越秀区遇见老袁馅饼店</v>
       </c>
       <c r="C44" t="str">
-        <v>广州市越秀区远记广潮仔海鲜馆（个体工商户）</v>
+        <v>广州市越秀区遇见老袁馅饼店（个体工商户）</v>
       </c>
       <c r="D44" t="str">
-        <v>已安装</v>
+        <v>用户拒绝</v>
       </c>
       <c r="E44" t="str">
-        <v>已填资料待推流</v>
+        <v>医国街全部要求装再装</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B45" t="str">
-        <v>潮汕壹粉道</v>
+        <v>威笑鸡煲档</v>
       </c>
       <c r="C45" t="str">
-        <v>广州市越秀区峰玲小食档（个体工商户）</v>
+        <v>广州市越秀区威笑鸡煲档（个体工商户）</v>
       </c>
       <c r="D45" t="str">
         <v>已安装</v>
       </c>
       <c r="E45" t="str">
-        <v>已填资料待推流</v>
+        <v>需荔湾整改，已填待推流</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B46" t="str">
         <v>铭记吃鸡</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B47" t="str">
         <v>广州市越秀区六榕街水啦餐饮服务店</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B48" t="str">
         <v>将军东路16号106号铺</v>
@@ -1511,9 +1511,26 @@
         <v>待跟进</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66">
+        <v>16</v>
+      </c>
+      <c r="B66" t="str">
+        <v>粤酥坊烘焙馆</v>
+      </c>
+      <c r="C66" t="str">
+        <v>广州市越秀区粤酥坊烘焙馆</v>
+      </c>
+      <c r="D66" t="str">
+        <v>已联系</v>
+      </c>
+      <c r="E66" t="str">
+        <v>9月4号受理</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E66"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
+++ b/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
@@ -1219,66 +1219,66 @@
         <v>已安装</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>食品安全证没下来</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B49" t="str">
-        <v>将相王者·黄焖鸡米饭（纪念堂店）</v>
+        <v>粤酥坊烘焙馆</v>
       </c>
       <c r="C49" t="str">
-        <v>广州市越秀区芋米餐饮店（个体工商户）</v>
+        <v>广州市越秀区粤酥坊烘焙馆（个体工商户）</v>
       </c>
       <c r="D49" t="str">
-        <v>已受理</v>
+        <v>已安装</v>
       </c>
       <c r="E49" t="str">
-        <v>摄像头未到，已填信息</v>
+        <v>食品安全证没下来</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="str">
-        <v>蒸武门</v>
+        <v>将相王者·黄焖鸡米饭（纪念堂店）</v>
       </c>
       <c r="C50" t="str">
-        <v>广州市蒸武门越来富餐饮有限公司</v>
+        <v>广州市越秀区芋米餐饮店（个体工商户）</v>
       </c>
       <c r="D50" t="str">
         <v>已受理</v>
       </c>
       <c r="E50" t="str">
-        <v>未装机，客户摄像头有问题</v>
+        <v>摄像头未到，已填信息</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" t="str">
-        <v>得宝未来城咖啡店</v>
+        <v>蒸武门</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>广州市蒸武门越来富餐饮有限公司</v>
       </c>
       <c r="D51" t="str">
-        <v>已联系</v>
+        <v>已受理</v>
       </c>
       <c r="E51" t="str">
-        <v>待拿资料受理</v>
+        <v>未装机，客户摄像头有问题</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" t="str">
-        <v>得宝未来城河南酒家</v>
+        <v>得宝未来城咖啡店</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1287,15 +1287,15 @@
         <v>已联系</v>
       </c>
       <c r="E52" t="str">
-        <v>已联系河南老板，回复要咨询一下</v>
+        <v>待拿资料受理</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="str">
-        <v>禧缘金宴</v>
+        <v>得宝未来城河南酒家</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1304,15 +1304,15 @@
         <v>已联系</v>
       </c>
       <c r="E53" t="str">
-        <v>待公司名资料盖章受理</v>
+        <v>已联系河南老板，回复要咨询一下</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54" t="str">
-        <v>迎宾馆</v>
+        <v>禧缘金宴</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1321,15 +1321,15 @@
         <v>已联系</v>
       </c>
       <c r="E54" t="str">
-        <v>待拿资料受理</v>
+        <v>待公司名资料盖章受理</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B55" t="str">
-        <v>美满湛江鸡</v>
+        <v>迎宾馆</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1338,15 +1338,15 @@
         <v>已联系</v>
       </c>
       <c r="E55" t="str">
-        <v>没有下文，老板不接电话</v>
+        <v>待拿资料受理</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B56" t="str">
-        <v>越秀渔村</v>
+        <v>美满湛江鸡</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1355,15 +1355,15 @@
         <v>已联系</v>
       </c>
       <c r="E56" t="str">
-        <v>11月装修后办理</v>
+        <v>没有下文，老板不接电话</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" t="str">
-        <v>盘福大厦咖啡店</v>
+        <v>越秀渔村</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1372,15 +1372,15 @@
         <v>已联系</v>
       </c>
       <c r="E57" t="str">
-        <v>待走第二次</v>
+        <v>11月装修后办理</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58" t="str">
-        <v>新文记</v>
+        <v>盘福大厦咖啡店</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1389,15 +1389,15 @@
         <v>已联系</v>
       </c>
       <c r="E58" t="str">
-        <v>等老板过来后再联系，暂无下文</v>
+        <v>待走第二次</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B59" t="str">
-        <v>东川饭局</v>
+        <v>新文记</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1406,12 +1406,12 @@
         <v>已联系</v>
       </c>
       <c r="E59" t="str">
-        <v>要中秋后联系</v>
+        <v>等老板过来后再联系，暂无下文</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" t="str">
         <v>东川饭局</v>
@@ -1423,35 +1423,35 @@
         <v>已联系</v>
       </c>
       <c r="E60" t="str">
-        <v>要中秋后联系</v>
+        <v>要国庆后联系</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" t="str">
-        <v>广州市越秀区天咖扉扒房</v>
+        <v>东川饭局</v>
       </c>
       <c r="C61" t="str">
-        <v>广州市越秀区天咖扉扒房</v>
+        <v/>
       </c>
       <c r="D61" t="str">
         <v>已联系</v>
       </c>
       <c r="E61" t="str">
-        <v>待跟进</v>
+        <v>要国庆后联系</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" t="str">
-        <v>田果小巷</v>
+        <v>广州市越秀区天咖扉扒房</v>
       </c>
       <c r="C62" t="str">
-        <v>广州果乐园管理有限公司</v>
+        <v>广州市越秀区天咖扉扒房</v>
       </c>
       <c r="D62" t="str">
         <v>已联系</v>
@@ -1462,13 +1462,13 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B63" t="str">
-        <v>慕茶山</v>
+        <v>田果小巷</v>
       </c>
       <c r="C63" t="str">
-        <v>广东慕茶山管理有限公司越秀区惠吉西第二分公司</v>
+        <v>广州果乐园管理有限公司</v>
       </c>
       <c r="D63" t="str">
         <v>已联系</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B64" t="str">
-        <v>赵大叔的店</v>
+        <v>慕茶山</v>
       </c>
       <c r="C64" t="str">
-        <v>广州市越秀区丁香食品店</v>
+        <v>广东慕茶山管理有限公司越秀区惠吉西第二分公司</v>
       </c>
       <c r="D64" t="str">
         <v>已联系</v>
@@ -1496,13 +1496,13 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B65" t="str">
-        <v>猪朋狗友咖啡店</v>
+        <v>赵大叔的店</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>广州市越秀区丁香食品店</v>
       </c>
       <c r="D65" t="str">
         <v>已联系</v>
@@ -1513,19 +1513,19 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B66" t="str">
-        <v>粤酥坊烘焙馆</v>
+        <v>猪朋狗友咖啡店</v>
       </c>
       <c r="C66" t="str">
-        <v>广州市越秀区粤酥坊烘焙馆</v>
+        <v/>
       </c>
       <c r="D66" t="str">
         <v>已联系</v>
       </c>
       <c r="E66" t="str">
-        <v>9月4号受理</v>
+        <v>待跟进</v>
       </c>
     </row>
   </sheetData>

--- a/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
+++ b/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -652,7 +652,7 @@
         <v>越秀区布论兹茶饮店</v>
       </c>
       <c r="C15" t="str">
-        <v>广州市越秀区布论兹茶饮店(个人独资)</v>
+        <v>越秀区布论兹茶饮店(个人独资)</v>
       </c>
       <c r="D15" t="str">
         <v>已上线</v>
@@ -737,7 +737,7 @@
         <v>窄巷口</v>
       </c>
       <c r="C20" t="str">
-        <v>广州市越秀区华记美食店（个体工商户）</v>
+        <v>广州市越秀区华记美食店(个体工商户)</v>
       </c>
       <c r="D20" t="str">
         <v>已上线</v>
@@ -1156,61 +1156,61 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B45" t="str">
-        <v>威笑鸡煲档</v>
+        <v>银记肠粉</v>
       </c>
       <c r="C45" t="str">
-        <v>广州市越秀区威笑鸡煲档（个体工商户）</v>
+        <v>广州市百灵餐饮有限公司</v>
       </c>
       <c r="D45" t="str">
-        <v>已安装</v>
+        <v>用户拒绝</v>
       </c>
       <c r="E45" t="str">
-        <v>需荔湾整改，已填待推流</v>
+        <v>客户微信拒绝，待现场沟通</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" t="str">
-        <v>铭记吃鸡</v>
+        <v>将相王者·黄焖鸡米饭（纪念堂店）</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>广州市越秀区芋米餐饮店（个体工商户）</v>
       </c>
       <c r="D46" t="str">
         <v>已安装</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>已装待推流</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="str">
-        <v>广州市越秀区六榕街水啦餐饮服务店</v>
+        <v>威笑鸡煲档</v>
       </c>
       <c r="C47" t="str">
-        <v>广州市越秀区六榕街水啦餐饮服务店（个体工商户）</v>
+        <v>广州市越秀区威笑鸡煲档（个体工商户）</v>
       </c>
       <c r="D47" t="str">
         <v>已安装</v>
       </c>
       <c r="E47" t="str">
-        <v>食品安全证没下来</v>
+        <v>需荔湾整改，已填待推流</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48" t="str">
-        <v>将军东路16号106号铺</v>
+        <v>铭记吃鸡</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1219,18 +1219,18 @@
         <v>已安装</v>
       </c>
       <c r="E48" t="str">
-        <v>食品安全证没下来</v>
+        <v>已装待推流</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B49" t="str">
-        <v>粤酥坊烘焙馆</v>
+        <v>广州市越秀区六榕街水啦餐饮服务店</v>
       </c>
       <c r="C49" t="str">
-        <v>广州市越秀区粤酥坊烘焙馆（个体工商户）</v>
+        <v>广州市越秀区六榕街水啦餐饮服务店（个体工商户）</v>
       </c>
       <c r="D49" t="str">
         <v>已安装</v>
@@ -1241,36 +1241,36 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B50" t="str">
-        <v>将相王者·黄焖鸡米饭（纪念堂店）</v>
+        <v>将军东路16号106号铺</v>
       </c>
       <c r="C50" t="str">
-        <v>广州市越秀区芋米餐饮店（个体工商户）</v>
+        <v/>
       </c>
       <c r="D50" t="str">
-        <v>已受理</v>
+        <v>已安装</v>
       </c>
       <c r="E50" t="str">
-        <v>摄像头未到，已填信息</v>
+        <v>食品安全证没下来</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B51" t="str">
-        <v>蒸武门</v>
+        <v>粤酥坊烘焙馆</v>
       </c>
       <c r="C51" t="str">
-        <v>广州市蒸武门越来富餐饮有限公司</v>
+        <v>广州市越秀区粤酥坊烘焙馆（个体工商户）</v>
       </c>
       <c r="D51" t="str">
-        <v>已受理</v>
+        <v>已安装</v>
       </c>
       <c r="E51" t="str">
-        <v>未装机，客户摄像头有问题</v>
+        <v>食品安全证没下来</v>
       </c>
     </row>
     <row r="52">
@@ -1278,24 +1278,24 @@
         <v>1</v>
       </c>
       <c r="B52" t="str">
-        <v>得宝未来城咖啡店</v>
+        <v>蒸武门</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>广州市蒸武门越来富餐饮有限公司</v>
       </c>
       <c r="D52" t="str">
-        <v>已联系</v>
+        <v>已受理</v>
       </c>
       <c r="E52" t="str">
-        <v>待拿资料受理</v>
+        <v>未装机，客户摄像头有问题</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" t="str">
-        <v>得宝未来城河南酒家</v>
+        <v>得宝未来城咖啡店</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1304,15 +1304,15 @@
         <v>已联系</v>
       </c>
       <c r="E53" t="str">
-        <v>已联系河南老板，回复要咨询一下</v>
+        <v>待拿资料受理</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B54" t="str">
-        <v>禧缘金宴</v>
+        <v>得宝未来城河南酒家</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1321,15 +1321,15 @@
         <v>已联系</v>
       </c>
       <c r="E54" t="str">
-        <v>待公司名资料盖章受理</v>
+        <v>已联系河南老板，回复要咨询一下</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55" t="str">
-        <v>迎宾馆</v>
+        <v>禧缘金宴</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1338,15 +1338,15 @@
         <v>已联系</v>
       </c>
       <c r="E55" t="str">
-        <v>待拿资料受理</v>
+        <v>待公司名资料盖章受理</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" t="str">
-        <v>美满湛江鸡</v>
+        <v>迎宾馆</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1355,15 +1355,15 @@
         <v>已联系</v>
       </c>
       <c r="E56" t="str">
-        <v>没有下文，老板不接电话</v>
+        <v>待拿资料受理</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B57" t="str">
-        <v>越秀渔村</v>
+        <v>美满湛江鸡</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1372,15 +1372,15 @@
         <v>已联系</v>
       </c>
       <c r="E57" t="str">
-        <v>11月装修后办理</v>
+        <v>没有下文，老板不接电话</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B58" t="str">
-        <v>盘福大厦咖啡店</v>
+        <v>越秀渔村</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1389,15 +1389,15 @@
         <v>已联系</v>
       </c>
       <c r="E58" t="str">
-        <v>待走第二次</v>
+        <v>11月装修后办理</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B59" t="str">
-        <v>新文记</v>
+        <v>盘福大厦咖啡店</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1406,15 +1406,15 @@
         <v>已联系</v>
       </c>
       <c r="E59" t="str">
-        <v>等老板过来后再联系，暂无下文</v>
+        <v>待走第二次</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" t="str">
-        <v>东川饭局</v>
+        <v>新文记</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1423,15 +1423,15 @@
         <v>已联系</v>
       </c>
       <c r="E60" t="str">
-        <v>要国庆后联系</v>
+        <v>等老板过来后再联系，暂无下文</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B61" t="str">
-        <v>东川饭局</v>
+        <v>东川饭局（盘福路）</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1445,30 +1445,30 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" t="str">
-        <v>广州市越秀区天咖扉扒房</v>
+        <v>东川饭局（百灵路）</v>
       </c>
       <c r="C62" t="str">
-        <v>广州市越秀区天咖扉扒房</v>
+        <v/>
       </c>
       <c r="D62" t="str">
         <v>已联系</v>
       </c>
       <c r="E62" t="str">
-        <v>待跟进</v>
+        <v>要国庆后联系</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" t="str">
-        <v>田果小巷</v>
+        <v>广州市越秀区天咖扉扒房</v>
       </c>
       <c r="C63" t="str">
-        <v>广州果乐园管理有限公司</v>
+        <v>广州市越秀区天咖扉扒房</v>
       </c>
       <c r="D63" t="str">
         <v>已联系</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B64" t="str">
-        <v>慕茶山</v>
+        <v>田果小巷</v>
       </c>
       <c r="C64" t="str">
-        <v>广东慕茶山管理有限公司越秀区惠吉西第二分公司</v>
+        <v>广州果乐园管理有限公司</v>
       </c>
       <c r="D64" t="str">
         <v>已联系</v>
@@ -1496,13 +1496,13 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B65" t="str">
-        <v>赵大叔的店</v>
+        <v>慕茶山</v>
       </c>
       <c r="C65" t="str">
-        <v>广州市越秀区丁香食品店</v>
+        <v>广东慕茶山管理有限公司越秀区惠吉西第二分公司</v>
       </c>
       <c r="D65" t="str">
         <v>已联系</v>
@@ -1513,13 +1513,13 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B66" t="str">
-        <v>猪朋狗友咖啡店</v>
+        <v>赵大叔的店</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>广州市越秀区丁香食品店</v>
       </c>
       <c r="D66" t="str">
         <v>已联系</v>
@@ -1528,9 +1528,26 @@
         <v>待跟进</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67">
+        <v>15</v>
+      </c>
+      <c r="B67" t="str">
+        <v>猪朋狗友咖啡店</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>已联系</v>
+      </c>
+      <c r="E67" t="str">
+        <v>待跟进</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E67"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
+++ b/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E69"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -632,10 +632,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>蜀渝拌·重庆凉拌菜（百灵路店）</v>
+        <v>将相王者·黄焖鸡米饭（纪念堂店）</v>
       </c>
       <c r="C14" t="str">
-        <v>广州市越秀区中琴凉菜店（个体工商户）</v>
+        <v>广州市越秀区芋米餐饮店（个体工商户）</v>
       </c>
       <c r="D14" t="str">
         <v>已上线</v>
@@ -649,10 +649,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>越秀区布论兹茶饮店</v>
+        <v>蜀渝拌·重庆凉拌菜（百灵路店）</v>
       </c>
       <c r="C15" t="str">
-        <v>越秀区布论兹茶饮店(个人独资)</v>
+        <v>广州市越秀区中琴凉菜店（个体工商户）</v>
       </c>
       <c r="D15" t="str">
         <v>已上线</v>
@@ -666,10 +666,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>惠吉东路15号咖啡店</v>
+        <v>越秀区布论兹茶饮店</v>
       </c>
       <c r="C16" t="str">
-        <v>广州市越秀区蜜糖埕食品店（个体工商户）</v>
+        <v>广州市越秀区布论兹茶饮店(个人独资)</v>
       </c>
       <c r="D16" t="str">
         <v>已上线</v>
@@ -683,10 +683,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>广州市越秀区卿予美甲店</v>
+        <v>惠吉东路15号咖啡店</v>
       </c>
       <c r="C17" t="str">
-        <v>广州市越秀区卿予美甲店(个体工商户)</v>
+        <v>广州市越秀区蜜糖埕食品店（个体工商户）</v>
       </c>
       <c r="D17" t="str">
         <v>已上线</v>
@@ -700,10 +700,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>广州市越秀区爽口凉拌菜馆</v>
+        <v>广州市越秀区卿予美甲店</v>
       </c>
       <c r="C18" t="str">
-        <v>广州市越秀区爽口凉拌菜馆（个体工商户）</v>
+        <v>广州市越秀区卿予美甲店(个体工商户)</v>
       </c>
       <c r="D18" t="str">
         <v>已上线</v>
@@ -717,10 +717,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>广州市越秀区坡里小吃店</v>
+        <v>广州市越秀区爽口凉拌菜馆</v>
       </c>
       <c r="C19" t="str">
-        <v>广州市越秀区坡里小吃店</v>
+        <v>广州市越秀区爽口凉拌菜馆（个体工商户）</v>
       </c>
       <c r="D19" t="str">
         <v>已上线</v>
@@ -734,10 +734,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>窄巷口</v>
+        <v>广州市越秀区坡里小吃店</v>
       </c>
       <c r="C20" t="str">
-        <v>广州市越秀区华记美食店(个体工商户)</v>
+        <v>广州市越秀区坡里小吃店</v>
       </c>
       <c r="D20" t="str">
         <v>已上线</v>
@@ -751,10 +751,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>创善烧鹅</v>
+        <v>窄巷口</v>
       </c>
       <c r="C21" t="str">
-        <v>广州市越秀区百煜餐饮店（个体工商户）</v>
+        <v>广州市越秀区华记美食店（个体工商户）</v>
       </c>
       <c r="D21" t="str">
         <v>已上线</v>
@@ -768,10 +768,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>炭火匠人</v>
+        <v>创善烧鹅</v>
       </c>
       <c r="C22" t="str">
-        <v>广州市越秀区万欢千膳餐饮店（个体工商户）</v>
+        <v>广州市越秀区百煜餐饮店（个体工商户）</v>
       </c>
       <c r="D22" t="str">
         <v>已上线</v>
@@ -785,10 +785,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>西华美食·老广烧腊(百灵路店)</v>
+        <v>炭火匠人</v>
       </c>
       <c r="C23" t="str">
-        <v>广州市西华美食品有限公司第一分店</v>
+        <v>广州市越秀区万欢千膳餐饮店（个体工商户）</v>
       </c>
       <c r="D23" t="str">
         <v>已上线</v>
@@ -802,10 +802,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>盘福路荔银肠粉店</v>
+        <v>西华美食·老广烧腊(百灵路店)</v>
       </c>
       <c r="C24" t="str">
-        <v>广州港旗餐饮管理有限公司</v>
+        <v>广州市西华美食品有限公司第一分店</v>
       </c>
       <c r="D24" t="str">
         <v>已上线</v>
@@ -819,10 +819,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>小东北</v>
+        <v>盘福路荔银肠粉店</v>
       </c>
       <c r="C25" t="str">
-        <v>广州市越秀区咱家饺子坊</v>
+        <v>广州港旗餐饮管理有限公司</v>
       </c>
       <c r="D25" t="str">
         <v>已上线</v>
@@ -836,10 +836,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>广潮仔</v>
+        <v>小东北</v>
       </c>
       <c r="C26" t="str">
-        <v>广州市越秀区远记广潮仔海鲜馆（个体工商户）</v>
+        <v>广州市越秀区咱家饺子坊</v>
       </c>
       <c r="D26" t="str">
         <v>已上线</v>
@@ -853,10 +853,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>潮汕壹粉道</v>
+        <v>广潮仔</v>
       </c>
       <c r="C27" t="str">
-        <v>广州市越秀区峰玲小食档（个体工商户）</v>
+        <v>广州市越秀区远记广潮仔海鲜馆（个体工商户）</v>
       </c>
       <c r="D27" t="str">
         <v>已上线</v>
@@ -870,10 +870,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>广州市越秀区味鲜小馆</v>
+        <v>潮汕壹粉道</v>
       </c>
       <c r="C28" t="str">
-        <v>广州市越秀区味鲜小馆（个体工商户）</v>
+        <v>广州市越秀区峰玲小食档（个体工商户）</v>
       </c>
       <c r="D28" t="str">
         <v>已上线</v>
@@ -887,10 +887,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>广州市越秀区滋味水饺店</v>
+        <v>广州市越秀区味鲜小馆</v>
       </c>
       <c r="C29" t="str">
-        <v>广州市越秀区滋味水饺店（个体工商户）</v>
+        <v>广州市越秀区味鲜小馆（个体工商户）</v>
       </c>
       <c r="D29" t="str">
         <v>已上线</v>
@@ -904,10 +904,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>广州市越秀区福华顺美食店</v>
+        <v>广州市越秀区滋味水饺店</v>
       </c>
       <c r="C30" t="str">
-        <v>广州市越秀区福华顺美食店（个体工商户）</v>
+        <v>广州市越秀区滋味水饺店（个体工商户）</v>
       </c>
       <c r="D30" t="str">
         <v>已上线</v>
@@ -921,10 +921,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>元气饭堂</v>
+        <v>广州市越秀区福华顺美食店</v>
       </c>
       <c r="C31" t="str">
-        <v>广州市豪哥烧腊有限公司</v>
+        <v>广州市越秀区福华顺美食店（个体工商户）</v>
       </c>
       <c r="D31" t="str">
         <v>已上线</v>
@@ -938,10 +938,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>新泰乐</v>
+        <v>元气饭堂</v>
       </c>
       <c r="C32" t="str">
-        <v>广州市越秀区盘福新泰乐菜馆</v>
+        <v>广州市豪哥烧腊有限公司</v>
       </c>
       <c r="D32" t="str">
         <v>已上线</v>
@@ -955,10 +955,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>顺德牛花猪杂粥</v>
+        <v>新泰乐</v>
       </c>
       <c r="C33" t="str">
-        <v>广州市越秀区捌记美食店（个体工商户）</v>
+        <v>广州市越秀区盘福新泰乐菜馆</v>
       </c>
       <c r="D33" t="str">
         <v>已上线</v>
@@ -972,10 +972,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>布豆咖啡</v>
+        <v>顺德牛花猪杂粥</v>
       </c>
       <c r="C34" t="str">
-        <v>广州市越秀区布豆食品店（个体工商户）</v>
+        <v>广州市越秀区捌记美食店（个体工商户）</v>
       </c>
       <c r="D34" t="str">
         <v>已上线</v>
@@ -989,10 +989,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>广州市越秀区市壹餐饮店（个体工商户）（荔银肠粉）</v>
+        <v>布豆咖啡</v>
       </c>
       <c r="C35" t="str">
-        <v>广州市越秀区市壹餐饮店（个体工商户）</v>
+        <v>广州市越秀区布豆食品店（个体工商户）</v>
       </c>
       <c r="D35" t="str">
         <v>已上线</v>
@@ -1003,33 +1003,33 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>吞口熊</v>
+        <v>广州市越秀区市壹餐饮店（个体工商户）（荔银肠粉）</v>
       </c>
       <c r="C36" t="str">
-        <v>广州市越秀区江南粥铺</v>
+        <v>广州市越秀区市壹餐饮店（个体工商户）</v>
       </c>
       <c r="D36" t="str">
-        <v>用户拒绝</v>
+        <v>已上线</v>
       </c>
       <c r="E36" t="str">
-        <v>已关门</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>叫了只炸鸡</v>
+        <v>铭记吃鸡</v>
       </c>
       <c r="C37" t="str">
-        <v>广州市越秀区童杨食品店</v>
+        <v>广州市越秀区汇越人家食府</v>
       </c>
       <c r="D37" t="str">
-        <v>用户拒绝</v>
+        <v>已上线</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1037,234 +1037,234 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>囍膳小厨 养生汤</v>
+        <v>粤酥坊烘焙馆</v>
       </c>
       <c r="C38" t="str">
-        <v>广州粤喜膳餐饮管理有限公司</v>
+        <v>广州市越秀区粤酥坊烘焙馆（个体工商户）</v>
       </c>
       <c r="D38" t="str">
-        <v>用户拒绝</v>
+        <v>已上线</v>
       </c>
       <c r="E38" t="str">
-        <v>二次联系后客户拒绝办理</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B39" t="str">
-        <v>广州港意头餐饮服务工作室</v>
+        <v>吞口熊</v>
       </c>
       <c r="C39" t="str">
-        <v>广州港意头餐饮服务工作室（个人独资）</v>
+        <v>广州市越秀区江南粥铺</v>
       </c>
       <c r="D39" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E39" t="str">
-        <v>已拒绝</v>
+        <v>已关门</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B40" t="str">
-        <v>广州市越秀区盛裕餐饮店</v>
+        <v>叫了只炸鸡</v>
       </c>
       <c r="C40" t="str">
-        <v>广州市越秀区盛裕餐饮店</v>
+        <v>广州市越秀区童杨食品店</v>
       </c>
       <c r="D40" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E40" t="str">
-        <v>客户反映已经有人帮他装了</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B41" t="str">
-        <v>王富贵（广州）餐饮管理服务有限公司</v>
+        <v>囍膳小厨 养生汤</v>
       </c>
       <c r="C41" t="str">
-        <v>王富贵（广州）餐饮管理服务有限公司</v>
+        <v>广州粤喜膳餐饮管理有限公司</v>
       </c>
       <c r="D41" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E41" t="str">
-        <v>已转荔湾跟进</v>
+        <v>二次联系后客户拒绝办理</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B42" t="str">
-        <v>肥俊牛肉饭</v>
+        <v>广州港意头餐饮服务工作室</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>广州港意头餐饮服务工作室（个人独资）</v>
       </c>
       <c r="D42" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E42" t="str">
-        <v>已转荔湾跟进</v>
+        <v>已拒绝</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B43" t="str">
-        <v>华辉拉肠</v>
+        <v>广州市越秀区盛裕餐饮店</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>广州市越秀区盛裕餐饮店</v>
       </c>
       <c r="D43" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E43" t="str">
-        <v>等集团统一通知</v>
+        <v>客户反映已经有人帮他装了</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B44" t="str">
-        <v>广州市越秀区遇见老袁馅饼店</v>
+        <v>王富贵（广州）餐饮管理服务有限公司</v>
       </c>
       <c r="C44" t="str">
-        <v>广州市越秀区遇见老袁馅饼店（个体工商户）</v>
+        <v>王富贵（广州）餐饮管理服务有限公司</v>
       </c>
       <c r="D44" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E44" t="str">
-        <v>医国街全部要求装再装</v>
+        <v>已转荔湾跟进</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B45" t="str">
-        <v>银记肠粉</v>
+        <v>肥俊牛肉饭</v>
       </c>
       <c r="C45" t="str">
-        <v>广州市百灵餐饮有限公司</v>
+        <v/>
       </c>
       <c r="D45" t="str">
         <v>用户拒绝</v>
       </c>
       <c r="E45" t="str">
-        <v>客户微信拒绝，待现场沟通</v>
+        <v>已转荔湾跟进</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B46" t="str">
-        <v>将相王者·黄焖鸡米饭（纪念堂店）</v>
+        <v>华辉拉肠</v>
       </c>
       <c r="C46" t="str">
-        <v>广州市越秀区芋米餐饮店（个体工商户）</v>
+        <v/>
       </c>
       <c r="D46" t="str">
-        <v>已安装</v>
+        <v>用户拒绝</v>
       </c>
       <c r="E46" t="str">
-        <v>已装待推流</v>
+        <v>等集团统一通知</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B47" t="str">
-        <v>威笑鸡煲档</v>
+        <v>广州市越秀区遇见老袁馅饼店</v>
       </c>
       <c r="C47" t="str">
-        <v>广州市越秀区威笑鸡煲档（个体工商户）</v>
+        <v>广州市越秀区遇见老袁馅饼店（个体工商户）</v>
       </c>
       <c r="D47" t="str">
-        <v>已安装</v>
+        <v>用户拒绝</v>
       </c>
       <c r="E47" t="str">
-        <v>需荔湾整改，已填待推流</v>
+        <v>医国街全部要求装再装</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B48" t="str">
-        <v>铭记吃鸡</v>
+        <v>银记肠粉</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>已安装</v>
+        <v>用户拒绝</v>
       </c>
       <c r="E48" t="str">
-        <v>已装待推流</v>
+        <v>客户微信拒绝，待现场沟通</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B49" t="str">
-        <v>广州市越秀区六榕街水啦餐饮服务店</v>
+        <v>威笑鸡煲档</v>
       </c>
       <c r="C49" t="str">
-        <v>广州市越秀区六榕街水啦餐饮服务店（个体工商户）</v>
+        <v>广州市越秀区威笑鸡煲档（个体工商户）</v>
       </c>
       <c r="D49" t="str">
         <v>已安装</v>
       </c>
       <c r="E49" t="str">
-        <v>食品安全证没下来</v>
+        <v>需荔湾整改，已填待推流</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B50" t="str">
-        <v>将军东路16号106号铺</v>
+        <v>东川饭局</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>广州市越秀区盘福烧腊店</v>
       </c>
       <c r="D50" t="str">
         <v>已安装</v>
       </c>
       <c r="E50" t="str">
-        <v>食品安全证没下来</v>
+        <v>已填写待推流</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B51" t="str">
-        <v>粤酥坊烘焙馆</v>
+        <v>卤水啦</v>
       </c>
       <c r="C51" t="str">
-        <v>广州市越秀区粤酥坊烘焙馆（个体工商户）</v>
+        <v>广州市越秀区六榕街水啦餐饮服务店（个体工商户）</v>
       </c>
       <c r="D51" t="str">
         <v>已安装</v>
@@ -1275,61 +1275,61 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B52" t="str">
-        <v>蒸武门</v>
+        <v>将军东路16号106号铺</v>
       </c>
       <c r="C52" t="str">
-        <v>广州市蒸武门越来富餐饮有限公司</v>
+        <v>广州忘本初未餐饮管理有限公司</v>
       </c>
       <c r="D52" t="str">
-        <v>已受理</v>
+        <v>已安装</v>
       </c>
       <c r="E52" t="str">
-        <v>未装机，客户摄像头有问题</v>
+        <v>食品安全证没下来</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B53" t="str">
-        <v>得宝未来城咖啡店</v>
+        <v>广伙计茶档</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>广州市百灵餐饮有限公司</v>
       </c>
       <c r="D53" t="str">
-        <v>已联系</v>
+        <v>已安装</v>
       </c>
       <c r="E53" t="str">
-        <v>待拿资料受理</v>
+        <v>食品安全证没下来</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="str">
-        <v>得宝未来城河南酒家</v>
+        <v>蒸武门</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>广州市蒸武门珍旺餐饮有限公司</v>
       </c>
       <c r="D54" t="str">
-        <v>已联系</v>
+        <v>已受理</v>
       </c>
       <c r="E54" t="str">
-        <v>已联系河南老板，回复要咨询一下</v>
+        <v>未装机，客户摄像头有问题</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B55" t="str">
-        <v>禧缘金宴</v>
+        <v>得宝未来城咖啡店</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1338,15 +1338,15 @@
         <v>已联系</v>
       </c>
       <c r="E55" t="str">
-        <v>待公司名资料盖章受理</v>
+        <v>待拿资料受理</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B56" t="str">
-        <v>迎宾馆</v>
+        <v>得宝未来城河南酒家</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1355,15 +1355,15 @@
         <v>已联系</v>
       </c>
       <c r="E56" t="str">
-        <v>待拿资料受理</v>
+        <v>已联系河南老板，回复要咨询一下</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B57" t="str">
-        <v>美满湛江鸡</v>
+        <v>禧缘金宴</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1372,15 +1372,15 @@
         <v>已联系</v>
       </c>
       <c r="E57" t="str">
-        <v>没有下文，老板不接电话</v>
+        <v>待公司名资料盖章受理</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B58" t="str">
-        <v>越秀渔村</v>
+        <v>迎宾馆</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1389,15 +1389,15 @@
         <v>已联系</v>
       </c>
       <c r="E58" t="str">
-        <v>11月装修后办理</v>
+        <v>待拿资料受理</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B59" t="str">
-        <v>盘福大厦咖啡店</v>
+        <v>美满湛江鸡</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1406,15 +1406,15 @@
         <v>已联系</v>
       </c>
       <c r="E59" t="str">
-        <v>待走第二次</v>
+        <v>没有下文，老板不接电话</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B60" t="str">
-        <v>新文记</v>
+        <v>越秀渔村</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1423,15 +1423,15 @@
         <v>已联系</v>
       </c>
       <c r="E60" t="str">
-        <v>等老板过来后再联系，暂无下文</v>
+        <v>11月装修后办理</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B61" t="str">
-        <v>东川饭局（盘福路）</v>
+        <v>盘福大厦咖啡店</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1440,15 +1440,15 @@
         <v>已联系</v>
       </c>
       <c r="E61" t="str">
-        <v>要国庆后联系</v>
+        <v>待走第二次</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B62" t="str">
-        <v>东川饭局（百灵路）</v>
+        <v>新文记</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1457,35 +1457,35 @@
         <v>已联系</v>
       </c>
       <c r="E62" t="str">
-        <v>要国庆后联系</v>
+        <v>等老板过来后再联系，暂无下文</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B63" t="str">
-        <v>广州市越秀区天咖扉扒房</v>
+        <v>东川饭局</v>
       </c>
       <c r="C63" t="str">
-        <v>广州市越秀区天咖扉扒房</v>
+        <v/>
       </c>
       <c r="D63" t="str">
         <v>已联系</v>
       </c>
       <c r="E63" t="str">
-        <v>待跟进</v>
+        <v>要国庆后联系</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B64" t="str">
-        <v>田果小巷</v>
+        <v>广州市越秀区天咖扉扒房</v>
       </c>
       <c r="C64" t="str">
-        <v>广州果乐园管理有限公司</v>
+        <v>广州市越秀区天咖扉扒房</v>
       </c>
       <c r="D64" t="str">
         <v>已联系</v>
@@ -1496,13 +1496,13 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B65" t="str">
-        <v>慕茶山</v>
+        <v>田果小巷</v>
       </c>
       <c r="C65" t="str">
-        <v>广东慕茶山管理有限公司越秀区惠吉西第二分公司</v>
+        <v>广州果乐园管理有限公司</v>
       </c>
       <c r="D65" t="str">
         <v>已联系</v>
@@ -1513,13 +1513,13 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B66" t="str">
-        <v>赵大叔的店</v>
+        <v>慕茶山</v>
       </c>
       <c r="C66" t="str">
-        <v>广州市越秀区丁香食品店</v>
+        <v>广东慕茶山管理有限公司越秀区惠吉西第二分公司</v>
       </c>
       <c r="D66" t="str">
         <v>已联系</v>
@@ -1530,13 +1530,13 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B67" t="str">
-        <v>猪朋狗友咖啡店</v>
+        <v>赵大叔的店</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>广州市越秀区丁香食品店</v>
       </c>
       <c r="D67" t="str">
         <v>已联系</v>
@@ -1545,9 +1545,43 @@
         <v>待跟进</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68">
+        <v>14</v>
+      </c>
+      <c r="B68" t="str">
+        <v>猪朋狗友咖啡店</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>已联系</v>
+      </c>
+      <c r="E68" t="str">
+        <v>待跟进</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>15</v>
+      </c>
+      <c r="B69" t="str">
+        <v>煲仔正</v>
+      </c>
+      <c r="C69" t="str">
+        <v>广州市科宁友明美食有限公司</v>
+      </c>
+      <c r="D69" t="str">
+        <v>已联系</v>
+      </c>
+      <c r="E69" t="str">
+        <v>待原有宽带迁移走后办理</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
+++ b/明厨亮灶专项行动·六榕所辖区跟进汇报.xlsx
@@ -35,13 +35,23 @@
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Noto Serif SC"/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+    </font>
+    <font>
+      <name val="Noto Serif SC"/>
+      <sz val="9"/>
+      <color rgb="FFE6E6E6"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,8 +74,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E72"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1474,7 +1490,7 @@
         <v>已联系</v>
       </c>
       <c r="E63" t="str">
-        <v>要国庆后联系</v>
+        <v>跟进中，待受理</v>
       </c>
     </row>
     <row r="64">
@@ -1579,9 +1595,45 @@
         <v>待原有宽带迁移走后办理</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70">
+        <v>16</v>
+      </c>
+      <c r="B70" t="str">
+        <v>广州几分野品牌管理有限公司</v>
+      </c>
+      <c r="C70" t="str">
+        <v>广州几分野品牌管理有限公司</v>
+      </c>
+      <c r="D70" t="str">
+        <v>已联系</v>
+      </c>
+      <c r="E70" t="str">
+        <v>需要确认是自购摄像头还是跟电信买</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>AI生成 | 生成内容标识 | 2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" hidden="1" ht="2" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>AIGC:36163cab-76e1-442d-a6ea-84480d511cd9</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>{"Label":"1","ContentProducer":"001191110102MAD55U9H0F10002","ProduceID":"36163cab-76e1-442d-a6ea-84480d511cd9","ReservedCode1":"3adc0713-ce2f-430c-99b9-957497b1a602","ContentPropagator":"001191110102MAD55U9H0F10002","PropagateID":"36163cab-76e1-442d-a6ea-84480d511cd9","ReservedCode2":"3adc0713-ce2f-430c-99b9-957497b1a602"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E70"/>
   </ignoredErrors>
 </worksheet>
 </file>